--- a/data/trans_camb/KIDM_A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,31</t>
+          <t>-3,88; 8,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 0,0</t>
+          <t>-10,26; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,66</t>
+          <t>-5,3; 5,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 6,29</t>
+          <t>-5,65; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 7,86</t>
+          <t>-5,37; 7,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -1,01</t>
+          <t>-9,72; -1,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,11</t>
+          <t>-3,05; 4,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,57</t>
+          <t>-4,29; 2,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,57</t>
+          <t>-5,66; 0,52</t>
         </is>
       </c>
     </row>
@@ -798,14 +798,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 612,82</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 366,04</t>
+          <t>-71,3; 369,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 206,56</t>
+          <t>-100,0; 348,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,24</t>
+          <t>-2,2; 5,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,42</t>
+          <t>-3,75; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 4,64</t>
+          <t>-2,92; 4,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,25</t>
+          <t>-2,29; 6,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,4</t>
+          <t>-5,46; 1,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,8</t>
+          <t>-4,24; 3,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,69</t>
+          <t>-1,12; 4,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,74</t>
+          <t>-3,37; 0,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,8</t>
+          <t>-2,85; 2,54</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 561,64</t>
+          <t>-62,55; 663,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 374,08</t>
+          <t>-34,78; 365,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,53; 104,86</t>
+          <t>-86,79; 135,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,93; 296,4</t>
+          <t>-84,27; 238,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 5,18</t>
+          <t>-2,4; 4,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 8,73</t>
+          <t>-0,31; 8,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,13</t>
+          <t>-4,57; 1,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,46</t>
+          <t>-2,4; 3,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,1</t>
+          <t>-3,31; 2,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,0</t>
+          <t>-5,46; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,39</t>
+          <t>-1,44; 3,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,89</t>
+          <t>-0,66; 4,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,38</t>
+          <t>-3,09; 0,37</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,63; —</t>
+          <t>-66,54; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,35</t>
+          <t>-4,05; 5,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,61</t>
+          <t>-6,94; 0,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,13</t>
+          <t>-5,79; 3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,76</t>
+          <t>0,78; 7,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,83</t>
+          <t>-0,53; 4,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,86</t>
+          <t>-2,84; 1,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,48</t>
+          <t>-1,8; 3,72</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 872,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 1348,08</t>
+          <t>-48,96; 1200,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,4</t>
+          <t>-1,15; 3,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,09</t>
+          <t>-2,56; 1,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,02</t>
+          <t>-2,67; 1,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,19</t>
+          <t>-0,22; 3,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,78</t>
+          <t>-2,01; 1,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,24</t>
+          <t>-2,49; 1,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,07</t>
+          <t>-0,36; 2,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,94</t>
+          <t>-1,65; 0,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,49</t>
+          <t>-1,92; 0,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 264,52</t>
+          <t>-42,2; 280,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 113,65</t>
+          <t>-74,92; 100,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 93,39</t>
+          <t>-88,86; 122,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 420,69</t>
+          <t>-20,01; 369,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 220,32</t>
+          <t>-74,79; 189,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 183,21</t>
+          <t>-86,81; 121,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 215,25</t>
+          <t>-14,0; 210,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 83,19</t>
+          <t>-60,39; 56,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 39,03</t>
+          <t>-75,98; 49,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 8,27</t>
+          <t>-3,69; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 0,0</t>
+          <t>-7,89; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 5,07</t>
+          <t>-5,21; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 6,06</t>
+          <t>-4,62; 6,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 7,43</t>
+          <t>-4,62; 7,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -1,01</t>
+          <t>-8,95; -1,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,72</t>
+          <t>-2,98; 5,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,66</t>
+          <t>-4,31; 3,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,52</t>
+          <t>-5,53; 0,62</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 612,82</t>
+          <t>-84,85; inf</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 369,68</t>
+          <t>-65,68; 374,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 348,29</t>
+          <t>-100,0; 308,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 258,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 5,18</t>
+          <t>-2,07; 5,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,77</t>
+          <t>-3,79; 1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 4,23</t>
+          <t>-3,12; 4,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,62</t>
+          <t>-2,13; 7,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,42</t>
+          <t>-5,47; 1,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,61</t>
+          <t>-4,98; 3,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,53</t>
+          <t>-1,18; 4,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,91</t>
+          <t>-3,41; 0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,54</t>
+          <t>-2,75; 3,05</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 663,65</t>
+          <t>-64,16; 728,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 365,78</t>
+          <t>-42,15; 344,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 135,56</t>
+          <t>-90,36; 95,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-84,27; 238,3</t>
+          <t>-81,06; 286,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,43</t>
+          <t>-2,36; 4,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 8,99</t>
+          <t>-0,71; 9,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,17</t>
+          <t>-5,06; 1,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,68</t>
+          <t>-2,3; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,08</t>
+          <t>-3,28; 2,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,0</t>
+          <t>-4,4; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,55</t>
+          <t>-1,7; 3,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,8</t>
+          <t>-0,86; 4,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,37</t>
+          <t>-3,51; 0,31</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,54; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,48</t>
+          <t>-4,05; 5,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,63</t>
+          <t>-7,02; 0,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,66</t>
+          <t>-5,15; 3,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,79</t>
+          <t>0,78; 7,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,92</t>
+          <t>-0,59; 4,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,06</t>
+          <t>-2,91; 0,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,72</t>
+          <t>-1,79; 3,67</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 872,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 1200,09</t>
+          <t>-50,44; 965,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,3</t>
+          <t>-1,03; 3,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,04</t>
+          <t>-2,4; 1,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,22</t>
+          <t>-2,77; 1,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,89</t>
+          <t>-0,22; 3,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,77</t>
+          <t>-1,9; 1,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,12</t>
+          <t>-2,25; 1,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,82</t>
+          <t>-0,08; 2,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,77</t>
+          <t>-1,68; 0,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,57</t>
+          <t>-2,02; 0,67</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 280,88</t>
+          <t>-41,45; 287,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 100,41</t>
+          <t>-74,76; 133,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 122,43</t>
+          <t>-89,07; 125,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 369,77</t>
+          <t>-19,03; 373,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 189,86</t>
+          <t>-72,48; 189,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,81; 121,92</t>
+          <t>-86,14; 146,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 210,43</t>
+          <t>-2,95; 227,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 56,47</t>
+          <t>-60,27; 65,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 49,9</t>
+          <t>-76,49; 58,66</t>
         </is>
       </c>
     </row>
